--- a/test/users.xlsx
+++ b/test/users.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCA6469-F622-495A-B8AB-9A5B6FA7ADD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329D49FF-F39C-4646-8BEC-3F5B2A0C42CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="18900" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,18 +28,6 @@
     <t>Jane</t>
   </si>
   <si>
-    <t>Doe</t>
-  </si>
-  <si>
-    <t>Smith</t>
-  </si>
-  <si>
-    <t>john.doe@example.com</t>
-  </si>
-  <si>
-    <t>jane.smith@example.com</t>
-  </si>
-  <si>
     <t>Pass@123</t>
   </si>
   <si>
@@ -56,13 +44,25 @@
   </si>
   <si>
     <t>password</t>
+  </si>
+  <si>
+    <t>john.does@example.com</t>
+  </si>
+  <si>
+    <t>jane.smithss@example.com</t>
+  </si>
+  <si>
+    <t>Doeeee</t>
+  </si>
+  <si>
+    <t>Smithaaaa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,6 +74,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -111,16 +119,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -428,16 +439,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -445,13 +456,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
         <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -459,16 +470,20 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{CE4C3BBA-90B1-4A12-A002-B8D4ABEB122A}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{56F06B29-C675-4689-866A-E0019E3323F3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/test/users.xlsx
+++ b/test/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329D49FF-F39C-4646-8BEC-3F5B2A0C42CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C1B0CD-87CB-4F93-BF46-98AAF9152365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>John</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t>Jane</t>
   </si>
@@ -56,6 +53,9 @@
   </si>
   <si>
     <t>Smithaaaa</t>
+  </si>
+  <si>
+    <t>Joh@n</t>
   </si>
 </sst>
 </file>
@@ -434,55 +434,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
+      <c r="A2" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{CE4C3BBA-90B1-4A12-A002-B8D4ABEB122A}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{56F06B29-C675-4689-866A-E0019E3323F3}"/>
+    <hyperlink ref="A2" r:id="rId3" xr:uid="{8BDC6076-FFF1-46C9-A69E-A7079AB09BF8}"/>
+    <hyperlink ref="C4" r:id="rId4" xr:uid="{9DA32327-4E83-4FAC-BE7E-CEBBED022EDF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
